--- a/Build/POS.xlsx
+++ b/Build/POS.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\StepperDriver\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62792DA9-C274-4377-99DC-9B42D2E0BB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{878BF4DE-C292-4129-A6A2-E6451C210318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{1B302167-B404-4462-BBF8-C97025A71357}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{A53FD2C3-29C1-44AB-93A3-6E80103F5E76}"/>
   </bookViews>
   <sheets>
-    <sheet name="POS" sheetId="1" r:id="rId1"/>
+    <sheet name="StepperDriver-all-pos" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="53">
+  <si>
+    <t>Ref</t>
+  </si>
   <si>
     <t>C1</t>
   </si>
@@ -102,6 +105,9 @@
     <t>D4</t>
   </si>
   <si>
+    <t>D5</t>
+  </si>
+  <si>
     <t>L1</t>
   </si>
   <si>
@@ -150,6 +156,9 @@
     <t>R15</t>
   </si>
   <si>
+    <t>R16</t>
+  </si>
+  <si>
     <t>SW1</t>
   </si>
   <si>
@@ -163,9 +172,6 @@
   </si>
   <si>
     <t>U2</t>
-  </si>
-  <si>
-    <t>Designator</t>
   </si>
   <si>
     <t>Mid X</t>
@@ -1037,30 +1043,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D24A6FE-7D3B-45FF-8AE6-DA64D1C934FB}">
-  <dimension ref="A1:E46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842DFFA9-968E-4124-B274-6736933BDEA6}">
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>147.6</v>
@@ -1072,12 +1078,12 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>140.80000000000001</v>
@@ -1089,12 +1095,12 @@
         <v>-90</v>
       </c>
       <c r="E3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>140.80000000000001</v>
@@ -1106,12 +1112,12 @@
         <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>156.4</v>
@@ -1123,12 +1129,12 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>156.4</v>
@@ -1140,12 +1146,12 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>171.6</v>
@@ -1157,12 +1163,12 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>167.2</v>
@@ -1174,12 +1180,12 @@
         <v>180</v>
       </c>
       <c r="E8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>147.5</v>
@@ -1191,12 +1197,12 @@
         <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>164.3</v>
@@ -1208,12 +1214,12 @@
         <v>180</v>
       </c>
       <c r="E10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>164.3</v>
@@ -1225,12 +1231,12 @@
         <v>180</v>
       </c>
       <c r="E11" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>144.9</v>
@@ -1242,12 +1248,12 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>135.55000000000001</v>
@@ -1259,12 +1265,12 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>135.55000000000001</v>
@@ -1276,12 +1282,12 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>135.55000000000001</v>
@@ -1293,12 +1299,12 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>135.55000000000001</v>
@@ -1310,12 +1316,12 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>148.9</v>
@@ -1327,12 +1333,12 @@
         <v>-90</v>
       </c>
       <c r="E17" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18">
         <v>136.80000000000001</v>
@@ -1344,12 +1350,12 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19">
         <v>162</v>
@@ -1361,12 +1367,12 @@
         <v>90</v>
       </c>
       <c r="E19" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20">
         <v>162</v>
@@ -1378,12 +1384,12 @@
         <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21">
         <v>162</v>
@@ -1395,12 +1401,12 @@
         <v>90</v>
       </c>
       <c r="E21" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22">
         <v>171.6</v>
@@ -1412,12 +1418,12 @@
         <v>-90</v>
       </c>
       <c r="E22" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23">
         <v>164.3</v>
@@ -1429,355 +1435,355 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24">
-        <v>171.6</v>
+        <v>168</v>
       </c>
       <c r="C24">
-        <v>-102.8</v>
+        <v>-79.3</v>
       </c>
       <c r="D24">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="E24" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25">
-        <v>168</v>
+        <v>171.6</v>
       </c>
       <c r="C25">
-        <v>-79.3</v>
+        <v>-102.8</v>
       </c>
       <c r="D25">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26">
-        <v>170.6</v>
+        <v>172.2</v>
       </c>
       <c r="C26">
-        <v>-95.4</v>
+        <v>-91.3</v>
       </c>
       <c r="D26">
         <v>180</v>
       </c>
       <c r="E26" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27">
-        <v>163.19999999999999</v>
+        <v>170.6</v>
       </c>
       <c r="C27">
-        <v>-99.6</v>
+        <v>-95.4</v>
       </c>
       <c r="D27">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="E27" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28">
         <v>163.19999999999999</v>
       </c>
       <c r="C28">
-        <v>-102.8</v>
+        <v>-99.6</v>
       </c>
       <c r="D28">
         <v>-90</v>
       </c>
       <c r="E28" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29">
-        <v>136.80000000000001</v>
+        <v>163.19999999999999</v>
       </c>
       <c r="C29">
-        <v>-79.5</v>
+        <v>-102.8</v>
       </c>
       <c r="D29">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="E29" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30">
-        <v>137.6</v>
+        <v>142.4</v>
       </c>
       <c r="C30">
-        <v>-106.8</v>
+        <v>-117.5</v>
       </c>
       <c r="D30">
         <v>90</v>
       </c>
       <c r="E30" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31">
-        <v>137.6</v>
+        <v>136.80000000000001</v>
       </c>
       <c r="C31">
-        <v>-114.6</v>
+        <v>-79.5</v>
       </c>
       <c r="D31">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="E31" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32">
-        <v>136.80000000000001</v>
+        <v>137.6</v>
       </c>
       <c r="C32">
-        <v>-91.93</v>
+        <v>-106.8</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E32" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33">
-        <v>136.80000000000001</v>
+        <v>137.6</v>
       </c>
       <c r="C33">
-        <v>-89.39</v>
+        <v>-114.6</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="E33" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34">
-        <v>157.4</v>
+        <v>136.80000000000001</v>
       </c>
       <c r="C34">
-        <v>-99.4</v>
+        <v>-91.93</v>
       </c>
       <c r="D34">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35">
-        <v>164.4</v>
+        <v>136.80000000000001</v>
       </c>
       <c r="C35">
-        <v>-78.5</v>
+        <v>-89.39</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36">
-        <v>164.4</v>
+        <v>157.4</v>
       </c>
       <c r="C36">
-        <v>-82.3</v>
+        <v>-99.4</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E36" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37">
         <v>164.4</v>
       </c>
       <c r="C37">
-        <v>-86.1</v>
+        <v>-78.5</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38">
         <v>164.4</v>
       </c>
       <c r="C38">
-        <v>-80.099999999999994</v>
+        <v>-82.3</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39">
         <v>164.4</v>
       </c>
       <c r="C39">
-        <v>-83.9</v>
+        <v>-86.1</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40">
-        <v>164.4</v>
+        <v>169</v>
       </c>
       <c r="C40">
-        <v>-87.7</v>
+        <v>-91.3</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41">
-        <v>142.4</v>
+        <v>164.4</v>
       </c>
       <c r="C41">
-        <v>-117.5</v>
+        <v>-80.099999999999994</v>
       </c>
       <c r="D41">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42">
-        <v>134.5</v>
+        <v>164.4</v>
       </c>
       <c r="C42">
-        <v>-122</v>
+        <v>-83.9</v>
       </c>
       <c r="D42">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43">
-        <v>150</v>
+        <v>164.4</v>
       </c>
       <c r="C43">
-        <v>-122</v>
+        <v>-87.7</v>
       </c>
       <c r="D43">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44">
-        <v>165.5</v>
+        <v>134.5</v>
       </c>
       <c r="C44">
         <v>-122</v>
@@ -1786,41 +1792,75 @@
         <v>180</v>
       </c>
       <c r="E44" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45">
-        <v>167.2</v>
+        <v>150</v>
       </c>
       <c r="C45">
-        <v>-102.8</v>
+        <v>-122</v>
       </c>
       <c r="D45">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="E45" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46">
+        <v>165.5</v>
+      </c>
+      <c r="C46">
+        <v>-122</v>
+      </c>
+      <c r="D46">
+        <v>180</v>
+      </c>
+      <c r="E46" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47">
+        <v>167.2</v>
+      </c>
+      <c r="C47">
+        <v>-102.8</v>
+      </c>
+      <c r="D47">
+        <v>-90</v>
+      </c>
+      <c r="E47" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48">
         <v>144.6</v>
       </c>
-      <c r="C46">
+      <c r="C48">
         <v>-110.7</v>
       </c>
-      <c r="D46">
+      <c r="D48">
         <v>90</v>
       </c>
-      <c r="E46" t="s">
-        <v>1</v>
+      <c r="E48" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Build/POS.xlsx
+++ b/Build/POS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\StepperDriver\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{878BF4DE-C292-4129-A6A2-E6451C210318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD2C9355-646E-45EA-BFDB-7495D1A0594A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{A53FD2C3-29C1-44AB-93A3-6E80103F5E76}"/>
+    <workbookView xWindow="2420" yWindow="2420" windowWidth="19200" windowHeight="11170" xr2:uid="{83DE084C-74F9-41C8-B2CC-CF4FDD51C72D}"/>
   </bookViews>
   <sheets>
     <sheet name="StepperDriver-all-pos" sheetId="1" r:id="rId1"/>
@@ -174,16 +174,16 @@
     <t>U2</t>
   </si>
   <si>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>Rotation</t>
+  </si>
+  <si>
     <t>Mid X</t>
   </si>
   <si>
     <t>Mid Y</t>
-  </si>
-  <si>
-    <t>Rotation</t>
-  </si>
-  <si>
-    <t>Layer</t>
   </si>
 </sst>
 </file>
@@ -1043,7 +1043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842DFFA9-968E-4124-B274-6736933BDEA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{077D5273-00E2-4600-82C1-A1468A70D3FC}">
   <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -1052,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" t="s">
         <v>49</v>
-      </c>
-      <c r="C1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">

--- a/Build/POS.xlsx
+++ b/Build/POS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\StepperDriver\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD2C9355-646E-45EA-BFDB-7495D1A0594A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02878C58-0543-4EC4-A8EF-40D16F8F574A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="2420" windowWidth="19200" windowHeight="11170" xr2:uid="{83DE084C-74F9-41C8-B2CC-CF4FDD51C72D}"/>
+    <workbookView xWindow="2420" yWindow="2420" windowWidth="19200" windowHeight="11170" xr2:uid="{321536CA-AF2C-4B14-9F87-9EB59C8DA0C7}"/>
   </bookViews>
   <sheets>
     <sheet name="StepperDriver-all-pos" sheetId="1" r:id="rId1"/>
@@ -174,16 +174,16 @@
     <t>U2</t>
   </si>
   <si>
+    <t>Mid X</t>
+  </si>
+  <si>
+    <t>Mid Y</t>
+  </si>
+  <si>
+    <t>Rotation</t>
+  </si>
+  <si>
     <t>Layer</t>
-  </si>
-  <si>
-    <t>Rotation</t>
-  </si>
-  <si>
-    <t>Mid X</t>
-  </si>
-  <si>
-    <t>Mid Y</t>
   </si>
 </sst>
 </file>
@@ -1043,7 +1043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{077D5273-00E2-4600-82C1-A1468A70D3FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE634389-93F2-46E7-9886-D020123D15DC}">
   <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -1052,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>52</v>
-      </c>
-      <c r="D1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -1647,13 +1647,13 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>157.4</v>
+        <v>144.6</v>
       </c>
       <c r="C36">
-        <v>-99.4</v>
+        <v>-100</v>
       </c>
       <c r="D36">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E36" t="s">
         <v>2</v>

--- a/Build/POS.xlsx
+++ b/Build/POS.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\StepperDriver\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02878C58-0543-4EC4-A8EF-40D16F8F574A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C7DD598-6684-463F-B0F1-7B0F3E02696B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="2420" windowWidth="19200" windowHeight="11170" xr2:uid="{321536CA-AF2C-4B14-9F87-9EB59C8DA0C7}"/>
+    <workbookView xWindow="2420" yWindow="2420" windowWidth="19200" windowHeight="11170" xr2:uid="{95C8B386-A4EE-444F-94E1-91B74D46C6ED}"/>
   </bookViews>
   <sheets>
-    <sheet name="StepperDriver-all-pos" sheetId="1" r:id="rId1"/>
+    <sheet name="POS" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -1043,7 +1043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE634389-93F2-46E7-9886-D020123D15DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8C0D695-480F-4138-9E96-B32B94B4BD89}">
   <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
